--- a/data-manipulation-scripts/sheets-cleanup/sheets/ESCOVA ARRANQUE - 02_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ESCOVA ARRANQUE - 02_02.xlsx
@@ -28,88 +28,88 @@
     <t>4045875046882</t>
   </si>
   <si>
-    <t>EA UNIK YBR125/ XTZ125/ FACTOR125</t>
+    <t>ESCOVA ARRANQUE  UNIK YBR125/ XTZ125/ FACTOR125</t>
   </si>
   <si>
     <t>7898485610899</t>
   </si>
   <si>
-    <t>EA MAGNETRON YBR125 2000 A 2007/ FACTOR125 2002 A 2015 90256010</t>
+    <t>ESCOVA ARRANQUE  MAGNETRON YBR125 2000 A 2007/ FACTOR125 2002 A 2015 90256010</t>
   </si>
   <si>
     <t>7908253805386</t>
   </si>
   <si>
-    <t>EA TMAC BIZ125 2011/ CG TITAN150 2004 A 2015/ FAN160/ NXR125-150-160</t>
+    <t>ESCOVA ARRANQUE  TMAC BIZ125 2011/ CG TITAN150 2004 A 2015/ FAN160/ NXR125-150-160</t>
   </si>
   <si>
     <t>7898508617911</t>
   </si>
   <si>
-    <t>EA MAGNETRON YS250 FAZER 2012 90203212</t>
+    <t>ESCOVA ARRANQUE  MAGNETRON YS250 FAZER 2012 90203212</t>
   </si>
   <si>
     <t>7895099126044</t>
   </si>
   <si>
-    <t>EA IRON YS150 FAZER 045410</t>
+    <t>ESCOVA ARRANQUE  IRON YS150 FAZER 045410</t>
   </si>
   <si>
     <t>751320980069</t>
   </si>
   <si>
-    <t>EA IRON CB300/ XRE300/ CRF250F 2008 EM DIANTE 017136</t>
+    <t>ESCOVA ARRANQUE  IRON CB300/ XRE300/ CRF250F 2008 EM DIANTE 017136</t>
   </si>
   <si>
     <t>751320980076</t>
   </si>
   <si>
-    <t>EA IRON YS250 FAZER/ XTZ250 2013 EM DIANTE 176831</t>
+    <t>ESCOVA ARRANQUE  IRON YS250 FAZER/ XTZ250 2013 EM DIANTE 176831</t>
   </si>
   <si>
     <t>7895099126112</t>
   </si>
   <si>
-    <t>EA IRON BIZES 045416</t>
+    <t>ESCOVA ARRANQUE  IRON BIZES 045416</t>
   </si>
   <si>
     <t>7908180600023</t>
   </si>
   <si>
-    <t>EA ZOUIL TITAN CG125 KS 2000 A 2004/ CBX250 2001 A 2008/ XTZ250 2007 A 2012/ NXR125-150 2003 A 2005</t>
+    <t>ESCOVA ARRANQUE  ZOUIL TITAN CG125 KS 2000 A 2004/ CBX250 2001 A 2008/ XTZ250 2007 A 2012/ NXR125-150 2003 A 2005</t>
   </si>
   <si>
     <t>7895099126105</t>
   </si>
   <si>
-    <t>EA IRON YES125/ INTRUDER125/ BURGMAN 045415</t>
+    <t>ESCOVA ARRANQUE  IRON YES125/ INTRUDER125/ BURGMAN 045415</t>
   </si>
   <si>
     <t>7898485610929</t>
   </si>
   <si>
-    <t>EA MAGNETRON CG TITAN150/ FAN125 2009 A 2013/ NXR125 2013 EM DIANTE 90205020</t>
+    <t>ESCOVA ARRANQUE  MAGNETRON CG TITAN150/ FAN125 2009 A 2013/ NXR125 2013 EM DIANTE 90205020</t>
   </si>
   <si>
     <t>7908193664043</t>
   </si>
   <si>
-    <t xml:space="preserve">EA SCT FAZER150 </t>
+    <t xml:space="preserve">ESCOVA ARRANQUE  SCT FAZER150 </t>
   </si>
   <si>
     <t>7899248106833</t>
   </si>
   <si>
-    <t>EA CONDOR CBX/ NX/ TITAN 2000 1101117</t>
+    <t>ESCOVA ARRANQUE  CONDOR CBX/ NX/ TITAN 2000 1101117</t>
   </si>
   <si>
-    <t>EA MAGNETRON FAN 2009/ CG TITAN150 90205050</t>
+    <t>ESCOVA ARRANQUE  MAGNETRON FAN 2009/ CG TITAN150 90205050</t>
   </si>
   <si>
-    <t>EA MAGENTRON 4 POLOS CG125 2000 EM DIANTE 90206080</t>
+    <t>ESCOVA ARRANQUE  MAGENTRON 4 POLOS CG125 2000 EM DIANTE 90206080</t>
   </si>
   <si>
-    <t xml:space="preserve">EA CONDOR YES125 </t>
+    <t xml:space="preserve">ESCOVA ARRANQUE  CONDOR YES125 </t>
   </si>
 </sst>
 </file>
